--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-15.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
         <v>3.65</v>
       </c>
       <c r="H2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -787,10 +787,10 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -799,13 +799,13 @@
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
         <v>1.37</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
@@ -963,7 +963,7 @@
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
         <v>8.199999999999999</v>
@@ -1002,7 +1002,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V4" t="n">
         <v>1.3</v>
@@ -1202,7 +1202,7 @@
         <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1262,7 +1262,7 @@
         <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
@@ -1274,10 +1274,10 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1292,10 +1292,10 @@
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
         <v>12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -1551,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
@@ -1656,7 +1656,7 @@
         <v>3.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>9.6</v>
@@ -1671,7 +1671,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>4.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H9" t="n">
         <v>5.2</v>
@@ -2136,37 +2136,37 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
         <v>5.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
         <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
         <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
         <v>1.6</v>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q11" t="n">
         <v>1.41</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
         <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I15" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
         <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W15" t="n">
         <v>1.34</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>3.45</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H17" t="n">
         <v>2.5</v>
@@ -3697,7 +3697,7 @@
         <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q17" t="n">
         <v>2.58</v>
@@ -3718,7 +3718,7 @@
         <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
         <v>9</v>
@@ -3793,7 +3793,7 @@
         <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
         <v>30</v>
@@ -3808,16 +3808,16 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB17" t="n">
         <v>15.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD17" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="BE17" t="n">
         <v>18</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -4267,34 +4267,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R20" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S20" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
         <v>1.06</v>
@@ -4303,7 +4303,7 @@
         <v>4.4</v>
       </c>
       <c r="X20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
         <v>50</v>
@@ -4333,7 +4333,7 @@
         <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
         <v>180</v>
@@ -4360,25 +4360,25 @@
         <v>24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
         <v>12.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX20" t="n">
         <v>7.8</v>
@@ -4387,10 +4387,10 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB20" t="n">
         <v>8.800000000000001</v>
@@ -4399,20 +4399,20 @@
         <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="O22" t="n">
         <v>1.39</v>
@@ -4670,7 +4670,7 @@
         <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.24</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.02</v>
       </c>
       <c r="G24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
         <v>3.6</v>
@@ -5043,7 +5043,7 @@
         <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
@@ -5055,16 +5055,16 @@
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5076,7 +5076,7 @@
         <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.38</v>
       </c>
       <c r="G25" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H25" t="n">
         <v>10.5</v>
@@ -5270,7 +5270,7 @@
         <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -6037,7 +6037,7 @@
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="U29" t="n">
         <v>2.24</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.42</v>
       </c>
       <c r="G30" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H30" t="n">
         <v>2.98</v>
@@ -6201,13 +6201,13 @@
         <v>3.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
         <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -6216,13 +6216,13 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
         <v>1.35</v>
@@ -6240,7 +6240,7 @@
         <v>1.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>3.9</v>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M33" t="n">
         <v>1.02</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
         <v>1.21</v>
       </c>
       <c r="M34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
         <v>1.69</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>1.64</v>
       </c>
       <c r="G35" t="n">
-        <v>110</v>
+        <v>2.28</v>
       </c>
       <c r="H35" t="n">
         <v>3.15</v>
       </c>
       <c r="I35" t="n">
-        <v>110</v>
+        <v>8.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="K35" t="n">
         <v>110</v>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O35" t="n">
         <v>1.02</v>
@@ -7210,7 +7210,7 @@
         <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
         <v>1.66</v>
       </c>
       <c r="O38" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P38" t="n">
         <v>1.66</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>1.27</v>
       </c>
       <c r="G39" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H39" t="n">
         <v>9.4</v>
@@ -7986,7 +7986,7 @@
         <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X39" t="n">
         <v>38</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
         <v>70</v>
       </c>
       <c r="AA40" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AB40" t="n">
         <v>12</v>
@@ -8225,7 +8225,7 @@
         <v>15</v>
       </c>
       <c r="AL40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM40" t="n">
         <v>95</v>
@@ -8243,10 +8243,10 @@
         <v>26</v>
       </c>
       <c r="AR40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT40" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
         <v>24</v>
       </c>
       <c r="AW40" t="n">
-        <v>11.5</v>
+        <v>75</v>
       </c>
       <c r="AX40" t="n">
         <v>9.4</v>
@@ -8288,11 +8288,11 @@
         <v>5.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
         <v>1.51</v>
       </c>
       <c r="O42" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P42" t="n">
         <v>1.51</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -8911,13 +8911,13 @@
         <v>1.86</v>
       </c>
       <c r="H44" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="K44" t="n">
         <v>110</v>
@@ -8932,7 +8932,7 @@
         <v>2.06</v>
       </c>
       <c r="O44" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P44" t="n">
         <v>2.06</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="I45" t="n">
         <v>1.76</v>
@@ -9114,7 +9114,7 @@
         <v>4.1</v>
       </c>
       <c r="K45" t="n">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -9123,7 +9123,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O45" t="n">
         <v>1.15</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G46" t="n">
         <v>3.85</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>3.55</v>
       </c>
       <c r="G47" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
@@ -9514,7 +9514,7 @@
         <v>1.9</v>
       </c>
       <c r="O47" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P47" t="n">
         <v>1.9</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -9705,10 +9705,10 @@
         <v>1.12</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O48" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P48" t="n">
         <v>1.58</v>
@@ -9723,10 +9723,10 @@
         <v>5.5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U48" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V48" t="n">
         <v>1.43</v>
@@ -9813,7 +9813,7 @@
         <v>44</v>
       </c>
       <c r="AX48" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY48" t="n">
         <v>12</v>
@@ -9837,14 +9837,14 @@
         <v>46</v>
       </c>
       <c r="BF48" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG48" t="n">
         <v>30</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -9875,19 +9875,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G49" t="n">
         <v>2.48</v>
       </c>
       <c r="H49" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I49" t="n">
         <v>4.2</v>
       </c>
       <c r="J49" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K49" t="n">
         <v>2.98</v>
@@ -9899,7 +9899,7 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O49" t="n">
         <v>1.46</v>
@@ -9914,13 +9914,13 @@
         <v>1.23</v>
       </c>
       <c r="S49" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T49" t="n">
         <v>1.82</v>
       </c>
       <c r="U49" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V49" t="n">
         <v>1.31</v>
@@ -9938,7 +9938,7 @@
         <v>32</v>
       </c>
       <c r="AA49" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB49" t="n">
         <v>9.4</v>
@@ -9947,10 +9947,10 @@
         <v>7.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE49" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF49" t="n">
         <v>16</v>
@@ -9992,10 +9992,10 @@
         <v>17</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU49" t="n">
         <v>6</v>
@@ -10004,7 +10004,7 @@
         <v>14</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX49" t="n">
         <v>11.5</v>
@@ -10013,32 +10013,32 @@
         <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB49" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC49" t="n">
         <v>23</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF49" t="n">
         <v>21</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G50" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H50" t="n">
         <v>3.05</v>
@@ -10117,10 +10117,10 @@
         <v>2.14</v>
       </c>
       <c r="V50" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W50" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X50" t="n">
         <v>12.5</v>
@@ -10174,7 +10174,7 @@
         <v>25</v>
       </c>
       <c r="AO50" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP50" t="n">
         <v>11.5</v>
@@ -10186,7 +10186,7 @@
         <v>18.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT50" t="n">
         <v>9.6</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G52" t="n">
         <v>2.44</v>
@@ -10469,7 +10469,7 @@
         <v>3.95</v>
       </c>
       <c r="J52" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K52" t="n">
         <v>3.3</v>
@@ -10481,13 +10481,13 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O52" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P52" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q52" t="n">
         <v>2.26</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
         <v>4.9</v>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>4.4</v>
@@ -10875,7 +10875,7 @@
         <v>1.23</v>
       </c>
       <c r="P54" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q54" t="n">
         <v>1.7</v>
@@ -10893,7 +10893,7 @@
         <v>2.3</v>
       </c>
       <c r="V54" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W54" t="n">
         <v>2.3</v>
@@ -10917,16 +10917,16 @@
         <v>9.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE54" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF54" t="n">
         <v>11.5</v>
       </c>
       <c r="AG54" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH54" t="n">
         <v>18</v>
@@ -10953,7 +10953,7 @@
         <v>50</v>
       </c>
       <c r="AP54" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ54" t="n">
         <v>19</v>
@@ -10962,7 +10962,7 @@
         <v>34</v>
       </c>
       <c r="AS54" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT54" t="n">
         <v>10</v>
@@ -10998,17 +10998,17 @@
         <v>26</v>
       </c>
       <c r="BE54" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF54" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG54" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
         <v>2.42</v>
       </c>
       <c r="H55" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I55" t="n">
         <v>3.4</v>
@@ -11075,7 +11075,7 @@
         <v>1.98</v>
       </c>
       <c r="R55" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
         <v>3.55</v>
@@ -11090,7 +11090,7 @@
         <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X55" t="n">
         <v>14</v>
@@ -11153,7 +11153,7 @@
         <v>12.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS55" t="n">
         <v>50</v>
@@ -11165,13 +11165,13 @@
         <v>7.2</v>
       </c>
       <c r="AV55" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW55" t="n">
         <v>34</v>
       </c>
       <c r="AX55" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY55" t="n">
         <v>10.5</v>
@@ -11180,10 +11180,10 @@
         <v>16</v>
       </c>
       <c r="BA55" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB55" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC55" t="n">
         <v>22</v>
@@ -11195,14 +11195,14 @@
         <v>65</v>
       </c>
       <c r="BF55" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G56" t="n">
         <v>2.64</v>
@@ -11281,7 +11281,7 @@
         <v>2.08</v>
       </c>
       <c r="V56" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W56" t="n">
         <v>1.61</v>
@@ -11371,7 +11371,7 @@
         <v>11</v>
       </c>
       <c r="AZ56" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA56" t="n">
         <v>46</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
         <v>1.69</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="R57" t="n">
         <v>1.25</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G58" t="n">
         <v>1.84</v>
@@ -11630,7 +11630,7 @@
         <v>4.8</v>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>4</v>
@@ -11657,13 +11657,13 @@
         <v>1.86</v>
       </c>
       <c r="R58" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S58" t="n">
         <v>3.15</v>
       </c>
       <c r="T58" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U58" t="n">
         <v>2.12</v>
@@ -11681,7 +11681,7 @@
         <v>19</v>
       </c>
       <c r="Z58" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA58" t="n">
         <v>140</v>
@@ -11780,11 +11780,11 @@
         <v>9.6</v>
       </c>
       <c r="BG58" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
         <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N60" t="n">
         <v>2.14</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -12400,13 +12400,13 @@
         <v>2.26</v>
       </c>
       <c r="G62" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H62" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I62" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>3.75</v>
@@ -12448,7 +12448,7 @@
         <v>1.41</v>
       </c>
       <c r="W62" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X62" t="n">
         <v>18</v>
@@ -12466,7 +12466,7 @@
         <v>12</v>
       </c>
       <c r="AC62" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD62" t="n">
         <v>14</v>
@@ -12502,10 +12502,10 @@
         <v>15.5</v>
       </c>
       <c r="AO62" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP62" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ62" t="n">
         <v>13.5</v>
@@ -12514,7 +12514,7 @@
         <v>21</v>
       </c>
       <c r="AS62" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT62" t="n">
         <v>11</v>
@@ -12532,7 +12532,7 @@
         <v>14</v>
       </c>
       <c r="AY62" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ62" t="n">
         <v>14.5</v>
@@ -12541,26 +12541,26 @@
         <v>36</v>
       </c>
       <c r="BB62" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC62" t="n">
         <v>20</v>
       </c>
       <c r="BD62" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE62" t="n">
         <v>34</v>
       </c>
       <c r="BF62" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG62" t="n">
         <v>25</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -12785,16 +12785,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G64" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H64" t="n">
         <v>2.08</v>
       </c>
       <c r="I64" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J64" t="n">
         <v>3.65</v>
@@ -12809,37 +12809,37 @@
         <v>1.05</v>
       </c>
       <c r="N64" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O64" t="n">
         <v>1.26</v>
       </c>
       <c r="P64" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R64" t="n">
         <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T64" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U64" t="n">
         <v>2.22</v>
       </c>
       <c r="V64" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W64" t="n">
         <v>1.35</v>
       </c>
       <c r="X64" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y64" t="n">
         <v>12</v>
@@ -12854,7 +12854,7 @@
         <v>16.5</v>
       </c>
       <c r="AC64" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD64" t="n">
         <v>11.5</v>
@@ -12887,7 +12887,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO64" t="n">
         <v>14.5</v>
@@ -12926,29 +12926,29 @@
         <v>14</v>
       </c>
       <c r="BA64" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB64" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD64" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC64" t="n">
+      <c r="BE64" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF64" t="n">
         <v>7</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG64" t="n">
         <v>10.5</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
         <v>3.15</v>
       </c>
       <c r="K65" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13003,7 +13003,7 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O65" t="n">
         <v>1.31</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -13188,10 +13188,10 @@
         <v>4.6</v>
       </c>
       <c r="K66" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L66" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M66" t="n">
         <v>1.01</v>
@@ -13200,7 +13200,7 @@
         <v>1.89</v>
       </c>
       <c r="O66" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P66" t="n">
         <v>1.89</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13761,7 @@
         <v>5.8</v>
       </c>
       <c r="H69" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I69" t="n">
         <v>2.04</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
         <v>1.04</v>
       </c>
       <c r="N71" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="O71" t="n">
         <v>1.2</v>
@@ -14188,7 +14188,7 @@
         <v>1.01</v>
       </c>
       <c r="U71" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V71" t="n">
         <v>1.41</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -14337,16 +14337,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G72" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H72" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>4</v>
@@ -14370,34 +14370,34 @@
         <v>2.6</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R72" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S72" t="n">
         <v>2.32</v>
       </c>
       <c r="T72" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U72" t="n">
         <v>2.32</v>
       </c>
       <c r="V72" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W72" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X72" t="n">
         <v>32</v>
       </c>
       <c r="Y72" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA72" t="n">
         <v>32</v>
@@ -14412,7 +14412,7 @@
         <v>14</v>
       </c>
       <c r="AE72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF72" t="n">
         <v>36</v>
@@ -14442,7 +14442,7 @@
         <v>28</v>
       </c>
       <c r="AO72" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP72" t="n">
         <v>22</v>
@@ -14454,7 +14454,7 @@
         <v>14.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT72" t="n">
         <v>17.5</v>
@@ -14481,16 +14481,16 @@
         <v>19.5</v>
       </c>
       <c r="BB72" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC72" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BD72" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BE72" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BF72" t="n">
         <v>16.5</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G73" t="n">
         <v>2.44</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -14743,22 +14743,22 @@
         <v>7</v>
       </c>
       <c r="L74" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M74" t="n">
         <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="O74" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P74" t="n">
         <v>1.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R74" t="n">
         <v>1.32</v>
@@ -14773,7 +14773,7 @@
         <v>1.54</v>
       </c>
       <c r="V74" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W74" t="n">
         <v>3.7</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -14919,19 +14919,19 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G75" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H75" t="n">
         <v>3.7</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J75" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
         <v>950</v>
@@ -14943,10 +14943,10 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="O75" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P75" t="n">
         <v>1.96</v>
@@ -14970,7 +14970,7 @@
         <v>1.27</v>
       </c>
       <c r="W75" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="G76" t="n">
         <v>2.04</v>
@@ -15122,7 +15122,7 @@
         <v>3.5</v>
       </c>
       <c r="I76" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>4.2</v>
@@ -15149,7 +15149,7 @@
         <v>1.41</v>
       </c>
       <c r="R76" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S76" t="n">
         <v>2</v>
@@ -15161,7 +15161,7 @@
         <v>2.56</v>
       </c>
       <c r="V76" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W76" t="n">
         <v>1.96</v>
@@ -15173,7 +15173,7 @@
         <v>28</v>
       </c>
       <c r="Z76" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA76" t="n">
         <v>75</v>
@@ -15188,7 +15188,7 @@
         <v>18</v>
       </c>
       <c r="AE76" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF76" t="n">
         <v>18.5</v>
@@ -15266,7 +15266,7 @@
         <v>20</v>
       </c>
       <c r="BE76" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF76" t="n">
         <v>6.4</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -15504,16 +15504,16 @@
         <v>3.95</v>
       </c>
       <c r="G78" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H78" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I78" t="n">
         <v>2.14</v>
       </c>
-      <c r="I78" t="n">
-        <v>2.16</v>
-      </c>
       <c r="J78" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K78" t="n">
         <v>3.6</v>
@@ -15531,7 +15531,7 @@
         <v>1.4</v>
       </c>
       <c r="P78" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q78" t="n">
         <v>2.18</v>
@@ -15549,10 +15549,10 @@
         <v>1.99</v>
       </c>
       <c r="V78" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W78" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X78" t="n">
         <v>12.5</v>
@@ -15612,7 +15612,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR78" t="n">
         <v>11</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
         <v>40</v>
       </c>
       <c r="AG80" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH80" t="n">
         <v>26</v>
@@ -16015,7 +16015,7 @@
         <v>7</v>
       </c>
       <c r="AV80" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW80" t="n">
         <v>21</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G81" t="n">
         <v>3.05</v>
@@ -16092,7 +16092,7 @@
         <v>2.92</v>
       </c>
       <c r="I81" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="J81" t="n">
         <v>2.3</v>
@@ -16131,7 +16131,7 @@
         <v>1.01</v>
       </c>
       <c r="V81" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W81" t="n">
         <v>1.51</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -16283,31 +16283,31 @@
         <v>2.64</v>
       </c>
       <c r="H82" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I82" t="n">
         <v>4.8</v>
       </c>
       <c r="J82" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K82" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L82" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M82" t="n">
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O82" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P82" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q82" t="n">
         <v>2.28</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
         <v>4</v>
       </c>
       <c r="X83" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y83" t="n">
         <v>44</v>
@@ -16540,7 +16540,7 @@
         <v>13</v>
       </c>
       <c r="AC83" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD83" t="n">
         <v>36</v>
@@ -16549,7 +16549,7 @@
         <v>130</v>
       </c>
       <c r="AF83" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG83" t="n">
         <v>11</v>
@@ -16579,7 +16579,7 @@
         <v>110</v>
       </c>
       <c r="AP83" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ83" t="n">
         <v>38</v>
@@ -16603,7 +16603,7 @@
         <v>85</v>
       </c>
       <c r="AX83" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY83" t="n">
         <v>10.5</v>
@@ -16621,20 +16621,20 @@
         <v>11.5</v>
       </c>
       <c r="BD83" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE83" t="n">
         <v>90</v>
       </c>
       <c r="BF83" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG83" t="n">
         <v>70</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -16719,13 +16719,13 @@
         <v>1.79</v>
       </c>
       <c r="X84" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y84" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z84" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA84" t="n">
         <v>1000</v>
@@ -16740,7 +16740,7 @@
         <v>16.5</v>
       </c>
       <c r="AE84" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF84" t="n">
         <v>14</v>
@@ -16755,10 +16755,10 @@
         <v>1000</v>
       </c>
       <c r="AJ84" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK84" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL84" t="n">
         <v>1000</v>
@@ -16767,7 +16767,7 @@
         <v>150</v>
       </c>
       <c r="AN84" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO84" t="n">
         <v>1000</v>
@@ -16776,13 +16776,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ84" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR84" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS84" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AT84" t="n">
         <v>8</v>
@@ -16794,7 +16794,7 @@
         <v>12.5</v>
       </c>
       <c r="AW84" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AX84" t="n">
         <v>11.5</v>
@@ -16803,13 +16803,13 @@
         <v>10</v>
       </c>
       <c r="AZ84" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA84" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC84" t="n">
         <v>17.5</v>
@@ -16818,17 +16818,17 @@
         <v>26</v>
       </c>
       <c r="BE84" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BF84" t="n">
         <v>18.5</v>
       </c>
       <c r="BG84" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -16862,16 +16862,16 @@
         <v>1.54</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H85" t="n">
         <v>4.5</v>
       </c>
       <c r="I85" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="J85" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K85" t="n">
         <v>7.4</v>
@@ -16883,22 +16883,22 @@
         <v>1.01</v>
       </c>
       <c r="N85" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O85" t="n">
         <v>1.29</v>
       </c>
       <c r="P85" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R85" t="n">
         <v>1.18</v>
       </c>
       <c r="S85" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T85" t="n">
         <v>1.01</v>
@@ -16907,10 +16907,10 @@
         <v>1.01</v>
       </c>
       <c r="V85" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="W85" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X85" t="n">
         <v>1000</v>
@@ -16967,52 +16967,52 @@
         <v>1000</v>
       </c>
       <c r="AP85" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ85" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR85" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS85" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AT85" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU85" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV85" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AW85" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AX85" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY85" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ85" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA85" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB85" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC85" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD85" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE85" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF85" t="n">
         <v>1.01</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
         <v>2.96</v>
       </c>
       <c r="I86" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>3.15</v>
@@ -17101,7 +17101,7 @@
         <v>1.01</v>
       </c>
       <c r="V86" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W86" t="n">
         <v>1.66</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -17441,10 +17441,10 @@
         </is>
       </c>
       <c r="F88" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G88" t="n">
         <v>2.14</v>
-      </c>
-      <c r="G88" t="n">
-        <v>2.16</v>
       </c>
       <c r="H88" t="n">
         <v>4.1</v>
@@ -17453,10 +17453,10 @@
         <v>4.2</v>
       </c>
       <c r="J88" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K88" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L88" t="n">
         <v>1.48</v>
@@ -17468,7 +17468,7 @@
         <v>3.3</v>
       </c>
       <c r="O88" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P88" t="n">
         <v>1.76</v>
@@ -17492,7 +17492,7 @@
         <v>1.32</v>
       </c>
       <c r="W88" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X88" t="n">
         <v>11</v>
@@ -17501,10 +17501,10 @@
         <v>13</v>
       </c>
       <c r="Z88" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA88" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB88" t="n">
         <v>8.199999999999999</v>
@@ -17513,7 +17513,7 @@
         <v>7.6</v>
       </c>
       <c r="AD88" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE88" t="n">
         <v>60</v>
@@ -17543,7 +17543,7 @@
         <v>140</v>
       </c>
       <c r="AN88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO88" t="n">
         <v>70</v>
@@ -17558,7 +17558,7 @@
         <v>25</v>
       </c>
       <c r="AS88" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AT88" t="n">
         <v>7.4</v>
@@ -17570,7 +17570,7 @@
         <v>15.5</v>
       </c>
       <c r="AW88" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX88" t="n">
         <v>11</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -17743,52 +17743,52 @@
         <v>1000</v>
       </c>
       <c r="AP89" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ89" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="AR89" t="n">
-        <v>90</v>
+        <v>1.03</v>
       </c>
       <c r="AS89" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="AT89" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU89" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV89" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AW89" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="AX89" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY89" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ89" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BA89" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BB89" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BC89" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD89" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE89" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BF89" t="n">
         <v>1.01</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17835,7 @@
         <v>12</v>
       </c>
       <c r="H90" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="I90" t="n">
         <v>1.76</v>
@@ -17853,13 +17853,13 @@
         <v>1.01</v>
       </c>
       <c r="N90" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="O90" t="n">
         <v>1.35</v>
       </c>
       <c r="P90" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q90" t="n">
         <v>2.06</v>
@@ -17937,52 +17937,52 @@
         <v>1000</v>
       </c>
       <c r="AP90" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ90" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR90" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS90" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT90" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU90" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV90" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW90" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX90" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AY90" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AZ90" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BA90" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB90" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BC90" t="n">
-        <v>85</v>
+        <v>1.03</v>
       </c>
       <c r="BD90" t="n">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="BE90" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BF90" t="n">
         <v>1.01</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -18047,10 +18047,10 @@
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O91" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P91" t="n">
         <v>1.46</v>
@@ -18131,52 +18131,52 @@
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ91" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR91" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS91" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AT91" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU91" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV91" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW91" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX91" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY91" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ91" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA91" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB91" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC91" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD91" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BE91" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF91" t="n">
         <v>1.01</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -18217,170 +18217,170 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G92" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H92" t="n">
-        <v>1.49</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
         <v>1000</v>
       </c>
       <c r="J92" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="K92" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P92" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q92" t="n">
         <v>2.14</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO92" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -18414,10 +18414,10 @@
         <v>2.38</v>
       </c>
       <c r="G93" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H93" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I93" t="n">
         <v>3.35</v>
@@ -18462,7 +18462,7 @@
         <v>1.42</v>
       </c>
       <c r="W93" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X93" t="n">
         <v>13</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -18608,13 +18608,13 @@
         <v>1.76</v>
       </c>
       <c r="G94" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H94" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I94" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J94" t="n">
         <v>3.8</v>
@@ -18632,13 +18632,13 @@
         <v>2.02</v>
       </c>
       <c r="O94" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P94" t="n">
         <v>2.02</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="R94" t="n">
         <v>1.35</v>
@@ -18656,7 +18656,7 @@
         <v>1.2</v>
       </c>
       <c r="W94" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X94" t="n">
         <v>1000</v>
@@ -18713,43 +18713,43 @@
         <v>1000</v>
       </c>
       <c r="AP94" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR94" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS94" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AT94" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU94" t="n">
         <v>7.4</v>
       </c>
       <c r="AV94" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW94" t="n">
         <v>42</v>
       </c>
       <c r="AX94" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY94" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ94" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA94" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB94" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BC94" t="n">
         <v>14.5</v>
@@ -18758,7 +18758,7 @@
         <v>26</v>
       </c>
       <c r="BE94" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BF94" t="n">
         <v>1.01</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
         <v>3.2</v>
       </c>
       <c r="J95" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K95" t="n">
         <v>3.3</v>
@@ -18823,13 +18823,13 @@
         <v>1.1</v>
       </c>
       <c r="N95" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="O95" t="n">
         <v>1.1</v>
       </c>
       <c r="P95" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q95" t="n">
         <v>2.4</v>
@@ -18907,52 +18907,52 @@
         <v>1000</v>
       </c>
       <c r="AP95" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ95" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR95" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS95" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AT95" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU95" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV95" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW95" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AX95" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY95" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ95" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA95" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB95" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BC95" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BD95" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BE95" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="BF95" t="n">
         <v>1.01</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -19038,7 +19038,7 @@
         <v>2.08</v>
       </c>
       <c r="U96" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V96" t="n">
         <v>1.05</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G97" t="n">
         <v>2.52</v>
@@ -19205,28 +19205,28 @@
         <v>4.2</v>
       </c>
       <c r="L97" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M97" t="n">
         <v>1.02</v>
       </c>
       <c r="N97" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="O97" t="n">
         <v>1.13</v>
       </c>
       <c r="P97" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q97" t="n">
         <v>1.41</v>
       </c>
       <c r="R97" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S97" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="T97" t="n">
         <v>1.39</v>
@@ -19286,22 +19286,22 @@
         <v>24</v>
       </c>
       <c r="AM97" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN97" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO97" t="n">
         <v>11.5</v>
       </c>
       <c r="AP97" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ97" t="n">
         <v>22</v>
       </c>
       <c r="AR97" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS97" t="n">
         <v>38</v>
@@ -19319,10 +19319,10 @@
         <v>22</v>
       </c>
       <c r="AX97" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY97" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ97" t="n">
         <v>11.5</v>
@@ -19334,7 +19334,7 @@
         <v>32</v>
       </c>
       <c r="BC97" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD97" t="n">
         <v>21</v>
@@ -19343,14 +19343,14 @@
         <v>30</v>
       </c>
       <c r="BF97" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG97" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -19683,52 +19683,52 @@
         <v>1000</v>
       </c>
       <c r="AP99" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ99" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR99" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AS99" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AT99" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU99" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV99" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW99" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AX99" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY99" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ99" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA99" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BB99" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC99" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD99" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BE99" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF99" t="n">
         <v>1.01</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -19877,52 +19877,52 @@
         <v>1000</v>
       </c>
       <c r="AP100" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ100" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR100" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS100" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AT100" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU100" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV100" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW100" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AX100" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY100" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ100" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BA100" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BB100" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BC100" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BD100" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE100" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF100" t="n">
         <v>1.01</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
         <v>2.32</v>
       </c>
       <c r="G101" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H101" t="n">
         <v>3.45</v>
@@ -20014,7 +20014,7 @@
         <v>1.37</v>
       </c>
       <c r="W101" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X101" t="n">
         <v>14</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20190,7 @@
         <v>1.92</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R102" t="n">
         <v>1.35</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -20396,7 +20396,7 @@
         <v>1.94</v>
       </c>
       <c r="U103" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="V103" t="n">
         <v>1.2</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G104" t="n">
         <v>1.42</v>
@@ -20554,13 +20554,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>130</v>
+        <v>18.5</v>
       </c>
       <c r="J104" t="n">
         <v>5.3</v>
       </c>
       <c r="K104" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="L104" t="n">
         <v>1.37</v>
@@ -20593,7 +20593,7 @@
         <v>1.01</v>
       </c>
       <c r="V104" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W104" t="n">
         <v>3.35</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -20763,10 +20763,10 @@
         <v>1.01</v>
       </c>
       <c r="N105" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O105" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P105" t="n">
         <v>1.39</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -20933,10 +20933,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G106" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H106" t="n">
         <v>3.5</v>
@@ -20954,7 +20954,7 @@
         <v>1.39</v>
       </c>
       <c r="M106" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N106" t="n">
         <v>4</v>
@@ -20978,13 +20978,13 @@
         <v>1.73</v>
       </c>
       <c r="U106" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V106" t="n">
         <v>1.38</v>
       </c>
       <c r="W106" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X106" t="n">
         <v>15</v>
@@ -21053,7 +21053,7 @@
         <v>44</v>
       </c>
       <c r="AT106" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU106" t="n">
         <v>7.4</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="F107" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G107" t="n">
         <v>4.4</v>
       </c>
-      <c r="G107" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I107" t="n">
         <v>2.04</v>
@@ -21145,7 +21145,7 @@
         <v>3.6</v>
       </c>
       <c r="L107" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M107" t="n">
         <v>1.09</v>
@@ -21160,13 +21160,13 @@
         <v>1.78</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R107" t="n">
         <v>1.29</v>
       </c>
       <c r="S107" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T107" t="n">
         <v>2</v>
@@ -21178,7 +21178,7 @@
         <v>1.96</v>
       </c>
       <c r="W107" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X107" t="n">
         <v>11</v>
@@ -21187,10 +21187,10 @@
         <v>7.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA107" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB107" t="n">
         <v>13.5</v>
@@ -21205,7 +21205,7 @@
         <v>23</v>
       </c>
       <c r="AF107" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG107" t="n">
         <v>17.5</v>
@@ -21223,19 +21223,19 @@
         <v>65</v>
       </c>
       <c r="AL107" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM107" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN107" t="n">
         <v>85</v>
       </c>
       <c r="AO107" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP107" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ107" t="n">
         <v>7.4</v>
@@ -21244,7 +21244,7 @@
         <v>10.5</v>
       </c>
       <c r="AS107" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT107" t="n">
         <v>12.5</v>
@@ -21283,14 +21283,14 @@
         <v>44</v>
       </c>
       <c r="BF107" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BG107" t="n">
         <v>17</v>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -21354,7 +21354,7 @@
         <v>2.16</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R108" t="n">
         <v>1.36</v>
@@ -21453,7 +21453,7 @@
         <v>1.92</v>
       </c>
       <c r="AX108" t="n">
-        <v>1.57</v>
+        <v>5.4</v>
       </c>
       <c r="AY108" t="n">
         <v>1.74</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -21521,7 +21521,7 @@
         <v>2.34</v>
       </c>
       <c r="H109" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I109" t="n">
         <v>6</v>
@@ -21533,152 +21533,152 @@
         <v>4.3</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P109" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q109" t="n">
         <v>2.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO109" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP109" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR109" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS109" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU109" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW109" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY109" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ109" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA109" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB109" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC109" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD109" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE109" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
         <v>3.45</v>
       </c>
       <c r="I110" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J110" t="n">
         <v>3.05</v>
@@ -21733,13 +21733,13 @@
         <v>1.01</v>
       </c>
       <c r="N110" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O110" t="n">
         <v>1.01</v>
       </c>
       <c r="P110" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q110" t="n">
         <v>2.8</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -21921,16 +21921,16 @@
         <v>85</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P111" t="n">
         <v>1.43</v>
@@ -21939,134 +21939,134 @@
         <v>2.32</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO111" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP111" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR111" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS111" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV111" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW111" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX111" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY111" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ111" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA111" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB111" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BC111" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BD111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG111" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -22115,16 +22115,16 @@
         <v>5.4</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P112" t="n">
         <v>1.42</v>
@@ -22133,134 +22133,134 @@
         <v>2.24</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO112" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP112" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR112" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS112" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW112" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX112" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY112" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ112" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA112" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB112" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC112" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD112" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE112" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -22291,7 +22291,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="G113" t="n">
         <v>3.3</v>
@@ -22303,22 +22303,22 @@
         <v>3.4</v>
       </c>
       <c r="J113" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="K113" t="n">
-        <v>5.1</v>
+        <v>110</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P113" t="n">
         <v>1.92</v>
@@ -22327,134 +22327,134 @@
         <v>1.66</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP113" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR113" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS113" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU113" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV113" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW113" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX113" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY113" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ113" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA113" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB113" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC113" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD113" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE113" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -22691,22 +22691,22 @@
         <v>6.2</v>
       </c>
       <c r="J115" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="K115" t="n">
         <v>4.8</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P115" t="n">
         <v>1.43</v>
@@ -22715,134 +22715,134 @@
         <v>2.32</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO115" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP115" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AU115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AW115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AX115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BB115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BD115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BE115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BF115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -22873,25 +22873,25 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G116" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="H116" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>4.3</v>
       </c>
       <c r="K116" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M116" t="n">
         <v>1.05</v>
@@ -22903,34 +22903,34 @@
         <v>1.27</v>
       </c>
       <c r="P116" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R116" t="n">
         <v>1.41</v>
       </c>
       <c r="S116" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T116" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U116" t="n">
         <v>2</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W116" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X116" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z116" t="n">
         <v>55</v>
@@ -22939,13 +22939,13 @@
         <v>200</v>
       </c>
       <c r="AB116" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC116" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD116" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE116" t="n">
         <v>95</v>
@@ -22954,10 +22954,10 @@
         <v>10.5</v>
       </c>
       <c r="AG116" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AH116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI116" t="n">
         <v>85</v>
@@ -22966,19 +22966,19 @@
         <v>16</v>
       </c>
       <c r="AK116" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL116" t="n">
         <v>34</v>
       </c>
       <c r="AM116" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN116" t="n">
         <v>9</v>
       </c>
       <c r="AO116" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP116" t="n">
         <v>16</v>
@@ -22987,56 +22987,56 @@
         <v>19</v>
       </c>
       <c r="AR116" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT116" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AS116" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT116" t="n">
-        <v>7.2</v>
       </c>
       <c r="AU116" t="n">
         <v>9</v>
       </c>
       <c r="AV116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW116" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AX116" t="n">
         <v>8.4</v>
       </c>
       <c r="AY116" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ116" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA116" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB116" t="n">
         <v>13</v>
       </c>
       <c r="BC116" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD116" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE116" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BF116" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG116" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -23070,10 +23070,10 @@
         <v>1.75</v>
       </c>
       <c r="G117" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H117" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I117" t="n">
         <v>5.9</v>
@@ -23085,7 +23085,7 @@
         <v>3.9</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M117" t="n">
         <v>1.08</v>
@@ -23115,10 +23115,10 @@
         <v>1.01</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X117" t="n">
         <v>1000</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -23473,16 +23473,16 @@
         <v>4.6</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P119" t="n">
         <v>1.7</v>
@@ -23491,134 +23491,134 @@
         <v>2.2</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG119" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH119" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AI119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK119" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL119" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP119" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AR119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AU119" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB119" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC119" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD119" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BE119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BG119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -23757,7 +23757,7 @@
         <v>250</v>
       </c>
       <c r="AP120" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ120" t="n">
         <v>4</v>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -23855,158 +23855,158 @@
         <v>1000</v>
       </c>
       <c r="J121" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K121" t="n">
         <v>1000</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P121" t="n">
         <v>1.24</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP121" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR121" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS121" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU121" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV121" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW121" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX121" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AY121" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ121" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA121" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB121" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BC121" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BD121" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BE121" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BF121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -24037,170 +24037,170 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G122" t="n">
         <v>5.2</v>
       </c>
       <c r="H122" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I122" t="n">
         <v>2.56</v>
       </c>
       <c r="J122" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="K122" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P122" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR122" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU122" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV122" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW122" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX122" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY122" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ122" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA122" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB122" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC122" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BD122" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BE122" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G126" t="n">
         <v>1.96</v>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
@@ -25170,7 +25170,7 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:53</t>
+          <t>2026-03-13 20:54:07</t>
         </is>
       </c>
     </row>
